--- a/research/traditional_assets/database/data/china/china_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/china/china_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07630000000000001</v>
+        <v>0.0654</v>
       </c>
       <c r="E2">
-        <v>0.075</v>
+        <v>0.07035</v>
+      </c>
+      <c r="F2">
+        <v>0.119</v>
       </c>
       <c r="G2">
-        <v>0.01003968316873537</v>
+        <v>0.05764986292469311</v>
       </c>
       <c r="H2">
-        <v>0.01003968316873537</v>
+        <v>0.05764986292469311</v>
       </c>
       <c r="I2">
-        <v>0.05671753879809141</v>
+        <v>0.05514438488491974</v>
       </c>
       <c r="J2">
-        <v>0.05287228104699561</v>
+        <v>0.04672996661770633</v>
       </c>
       <c r="K2">
-        <v>7310.1</v>
+        <v>7117.8</v>
       </c>
       <c r="L2">
-        <v>0.04828361048142923</v>
+        <v>0.04719103358427894</v>
       </c>
       <c r="M2">
-        <v>2825.42</v>
+        <v>2127.5</v>
       </c>
       <c r="N2">
-        <v>0.05306899822503545</v>
+        <v>0.04179567171685421</v>
       </c>
       <c r="O2">
-        <v>0.3865090764832219</v>
+        <v>0.2988985360645143</v>
       </c>
       <c r="P2">
-        <v>2825.42</v>
+        <v>2127.5</v>
       </c>
       <c r="Q2">
-        <v>0.05306899822503545</v>
+        <v>0.04179567171685421</v>
       </c>
       <c r="R2">
-        <v>0.3865090764832219</v>
+        <v>0.2988985360645143</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6362.48</v>
+        <v>4452.3</v>
       </c>
       <c r="V2">
-        <v>0.1195045125421437</v>
+        <v>0.08746738857106934</v>
       </c>
       <c r="W2">
-        <v>0.08755076013685212</v>
+        <v>0.1127553934927922</v>
       </c>
       <c r="X2">
-        <v>0.0635236387354311</v>
+        <v>0.1023650873741052</v>
       </c>
       <c r="Y2">
-        <v>0.02402712140142102</v>
+        <v>0.01039030611868698</v>
       </c>
       <c r="Z2">
-        <v>1.947139638043605</v>
+        <v>1.797476636182277</v>
       </c>
       <c r="AA2">
-        <v>0.05759683236331136</v>
+        <v>0.08465892576715235</v>
       </c>
       <c r="AB2">
-        <v>0.05315790549742664</v>
+        <v>0.08580520255436383</v>
       </c>
       <c r="AC2">
-        <v>0.004502285517698219</v>
+        <v>-0.001146276787211485</v>
       </c>
       <c r="AD2">
-        <v>27165.3</v>
+        <v>21211.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>27165.3</v>
+        <v>21211.6</v>
       </c>
       <c r="AG2">
-        <v>20802.82</v>
+        <v>16759.3</v>
       </c>
       <c r="AH2">
-        <v>0.3378524932281005</v>
+        <v>0.2941398341514824</v>
       </c>
       <c r="AI2">
-        <v>0.2569828755654696</v>
+        <v>0.2240791369642472</v>
       </c>
       <c r="AJ2">
-        <v>0.2809547167793124</v>
+        <v>0.2476925646266647</v>
       </c>
       <c r="AK2">
-        <v>0.209397407769926</v>
+        <v>0.1857832209460485</v>
       </c>
       <c r="AL2">
-        <v>1273.12</v>
+        <v>916.2</v>
       </c>
       <c r="AM2">
-        <v>1273.12</v>
+        <v>916.2</v>
       </c>
       <c r="AN2">
-        <v>2.904019293635709</v>
+        <v>2.346052602473068</v>
       </c>
       <c r="AO2">
-        <v>6.744839449541284</v>
+        <v>9.078148875791314</v>
       </c>
       <c r="AP2">
-        <v>2.223858769902442</v>
+        <v>1.853617802552702</v>
       </c>
       <c r="AQ2">
-        <v>6.744839449541284</v>
+        <v>9.078148875791314</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08550000000000001</v>
+        <v>0.0747</v>
       </c>
       <c r="E3">
-        <v>0.06</v>
+        <v>0.0506</v>
+      </c>
+      <c r="F3">
+        <v>0.119</v>
       </c>
       <c r="G3">
-        <v>0.06093849618251084</v>
+        <v>0.06135823160550052</v>
       </c>
       <c r="H3">
-        <v>0.06093849618251084</v>
+        <v>0.06135823160550052</v>
       </c>
       <c r="I3">
-        <v>0.06570917987581774</v>
+        <v>0.0569406626042843</v>
       </c>
       <c r="J3">
-        <v>0.05561686515588433</v>
+        <v>0.04919966480653237</v>
       </c>
       <c r="K3">
-        <v>3746</v>
+        <v>3716.8</v>
       </c>
       <c r="L3">
-        <v>0.05882482263044004</v>
+        <v>0.0577328426994391</v>
       </c>
       <c r="M3">
-        <v>1588</v>
+        <v>1245.2</v>
       </c>
       <c r="N3">
-        <v>0.08739632693270814</v>
+        <v>0.05890812754281389</v>
       </c>
       <c r="O3">
-        <v>0.4239188467698879</v>
+        <v>0.3350193715023676</v>
       </c>
       <c r="P3">
-        <v>1588</v>
+        <v>1245.2</v>
       </c>
       <c r="Q3">
-        <v>0.08739632693270814</v>
+        <v>0.05890812754281389</v>
       </c>
       <c r="R3">
-        <v>0.4239188467698879</v>
+        <v>0.3350193715023676</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2235.1</v>
+        <v>1685.5</v>
       </c>
       <c r="V3">
-        <v>0.1230097798030831</v>
+        <v>0.07973791276374302</v>
       </c>
       <c r="W3">
-        <v>0.1549912905321257</v>
+        <v>0.1231299277810906</v>
       </c>
       <c r="X3">
-        <v>0.06503332956000911</v>
+        <v>0.09482456049449245</v>
       </c>
       <c r="Y3">
-        <v>0.08995796097211663</v>
+        <v>0.02830536728659813</v>
       </c>
       <c r="Z3">
-        <v>2.237099386278925</v>
+        <v>1.829045720958114</v>
       </c>
       <c r="AA3">
-        <v>0.1244204549069866</v>
+        <v>0.08998843638696156</v>
       </c>
       <c r="AB3">
-        <v>0.05276308843625811</v>
+        <v>0.08680738240220134</v>
       </c>
       <c r="AC3">
-        <v>0.07165736647072848</v>
+        <v>0.003181053984760221</v>
       </c>
       <c r="AD3">
-        <v>7247.4</v>
+        <v>3777.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7247.4</v>
+        <v>3777.6</v>
       </c>
       <c r="AG3">
-        <v>5012.299999999999</v>
+        <v>2092.1</v>
       </c>
       <c r="AH3">
-        <v>0.2851342578931838</v>
+        <v>0.1516158551269084</v>
       </c>
       <c r="AI3">
-        <v>0.1915229288943973</v>
+        <v>0.1076681031534305</v>
       </c>
       <c r="AJ3">
-        <v>0.2162114362619919</v>
+        <v>0.09005987920844077</v>
       </c>
       <c r="AK3">
-        <v>0.1407720090547045</v>
+        <v>0.06263753701336224</v>
       </c>
       <c r="AL3">
-        <v>275.4</v>
+        <v>148.7</v>
       </c>
       <c r="AM3">
-        <v>275.4</v>
+        <v>148.7</v>
       </c>
       <c r="AN3">
-        <v>1.586940813243119</v>
+        <v>0.9368815257558096</v>
       </c>
       <c r="AO3">
-        <v>15.19389978213508</v>
+        <v>24.65232010759919</v>
       </c>
       <c r="AP3">
-        <v>1.097527863539819</v>
+        <v>0.5188611393566628</v>
       </c>
       <c r="AQ3">
-        <v>15.19389978213508</v>
+        <v>24.65232010759919</v>
       </c>
     </row>
     <row r="4">
@@ -856,46 +862,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.06709999999999999</v>
+        <v>0.0561</v>
       </c>
       <c r="E4">
-        <v>0.09</v>
+        <v>0.0901</v>
       </c>
       <c r="G4">
-        <v>0.04743426974630467</v>
+        <v>0.05488824780046779</v>
       </c>
       <c r="H4">
-        <v>0.04743426974630467</v>
+        <v>0.05488824780046779</v>
       </c>
       <c r="I4">
-        <v>0.04617962087180479</v>
+        <v>0.05380670027368358</v>
       </c>
       <c r="J4">
-        <v>0.04164189431623511</v>
+        <v>0.04470103556475404</v>
       </c>
       <c r="K4">
-        <v>3425.5</v>
+        <v>3401</v>
       </c>
       <c r="L4">
-        <v>0.03657701889020702</v>
+        <v>0.03934056832719878</v>
       </c>
       <c r="M4">
-        <v>1235.3</v>
+        <v>882.3</v>
       </c>
       <c r="N4">
-        <v>0.04273788147702229</v>
+        <v>0.02964279474808832</v>
       </c>
       <c r="O4">
-        <v>0.3606188877536126</v>
+        <v>0.2594236989120847</v>
       </c>
       <c r="P4">
-        <v>1235.3</v>
+        <v>882.3</v>
       </c>
       <c r="Q4">
-        <v>0.04273788147702229</v>
+        <v>0.02964279474808832</v>
       </c>
       <c r="R4">
-        <v>0.3606188877536126</v>
+        <v>0.2594236989120847</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,326 +910,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2896.3</v>
+        <v>2766.8</v>
       </c>
       <c r="V4">
-        <v>0.1002037773187887</v>
+        <v>0.09295668651140289</v>
       </c>
       <c r="W4">
-        <v>0.1176088882174812</v>
+        <v>0.1023808592044938</v>
       </c>
       <c r="X4">
-        <v>0.07187681960303245</v>
+        <v>0.109905614253718</v>
       </c>
       <c r="Y4">
-        <v>0.04573206861444871</v>
+        <v>-0.007524755049224188</v>
       </c>
       <c r="Z4">
-        <v>2.009261960952585</v>
+        <v>1.774666160304638</v>
       </c>
       <c r="AA4">
-        <v>0.08366947423161886</v>
+        <v>0.07932941514734314</v>
       </c>
       <c r="AB4">
-        <v>0.05248214312090273</v>
+        <v>0.08480302270652633</v>
       </c>
       <c r="AC4">
-        <v>0.03118733111071613</v>
+        <v>-0.005473607559183191</v>
       </c>
       <c r="AD4">
-        <v>18390.7</v>
+        <v>17434</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>18390.7</v>
+        <v>17434</v>
       </c>
       <c r="AG4">
-        <v>15494.4</v>
+        <v>14667.2</v>
       </c>
       <c r="AH4">
-        <v>0.3888524742677842</v>
+        <v>0.3693769280314587</v>
       </c>
       <c r="AI4">
-        <v>0.2909340859259071</v>
+        <v>0.2926365827620704</v>
       </c>
       <c r="AJ4">
-        <v>0.34898476299875</v>
+        <v>0.3301074010389002</v>
       </c>
       <c r="AK4">
-        <v>0.2568857837765248</v>
+        <v>0.2581853515652505</v>
       </c>
       <c r="AL4">
-        <v>944.2</v>
+        <v>767.5</v>
       </c>
       <c r="AM4">
-        <v>944.2</v>
+        <v>767.5</v>
       </c>
       <c r="AN4">
-        <v>3.897903817214556</v>
+        <v>3.480326592537879</v>
       </c>
       <c r="AO4">
-        <v>4.580385511544164</v>
+        <v>6.060716612377851</v>
       </c>
       <c r="AP4">
-        <v>3.284033827176194</v>
+        <v>2.927993931287805</v>
       </c>
       <c r="AQ4">
-        <v>4.580385511544164</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ZhongAn Online P &amp; C Insurance Co., Ltd. (SEHK:6060)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="G5">
-        <v>0.01741803278688525</v>
-      </c>
-      <c r="H5">
-        <v>0.01741803278688525</v>
-      </c>
-      <c r="I5">
-        <v>0.02531729243786356</v>
-      </c>
-      <c r="J5">
-        <v>0.02531729243786356</v>
-      </c>
-      <c r="K5">
-        <v>126.8</v>
-      </c>
-      <c r="L5">
-        <v>0.04190904283447911</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>-0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>-0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>1221.8</v>
-      </c>
-      <c r="V5">
-        <v>0.2391887394530256</v>
-      </c>
-      <c r="W5">
-        <v>0.05749263205622308</v>
-      </c>
-      <c r="X5">
-        <v>0.06201394791085307</v>
-      </c>
-      <c r="Y5">
-        <v>-0.004521315854629997</v>
-      </c>
-      <c r="Z5">
-        <v>1.245164370256967</v>
-      </c>
-      <c r="AA5">
-        <v>0.03152419049500386</v>
-      </c>
-      <c r="AB5">
-        <v>0.05370695057032356</v>
-      </c>
-      <c r="AC5">
-        <v>-0.02218276007531969</v>
-      </c>
-      <c r="AD5">
-        <v>1502.4</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>1502.4</v>
-      </c>
-      <c r="AG5">
-        <v>280.6000000000001</v>
-      </c>
-      <c r="AH5">
-        <v>0.2272747901066485</v>
-      </c>
-      <c r="AI5">
-        <v>0.3444607483492296</v>
-      </c>
-      <c r="AJ5">
-        <v>0.05207192829439384</v>
-      </c>
-      <c r="AK5">
-        <v>0.08936874960188551</v>
-      </c>
-      <c r="AL5">
-        <v>52.3</v>
-      </c>
-      <c r="AM5">
-        <v>52.3</v>
-      </c>
-      <c r="AN5">
-        <v>21.07152875175316</v>
-      </c>
-      <c r="AO5">
-        <v>1.464627151051625</v>
-      </c>
-      <c r="AP5">
-        <v>3.935483870967744</v>
-      </c>
-      <c r="AQ5">
-        <v>1.464627151051625</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Xishui Strong Year Co.,Ltd Inner Mongolia (SHSE:600291)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="G6">
-        <v>0.7652449574156964</v>
-      </c>
-      <c r="H6">
-        <v>0.7652449574156964</v>
-      </c>
-      <c r="I6">
-        <v>-0.0001328317724669874</v>
-      </c>
-      <c r="J6">
-        <v>-0.0001302636915326256</v>
-      </c>
-      <c r="K6">
-        <v>11.8</v>
-      </c>
-      <c r="L6">
-        <v>-0.001317155390849119</v>
-      </c>
-      <c r="M6">
-        <v>2.12</v>
-      </c>
-      <c r="N6">
-        <v>0.002003402003402004</v>
-      </c>
-      <c r="O6">
-        <v>0.1796610169491525</v>
-      </c>
-      <c r="P6">
-        <v>2.12</v>
-      </c>
-      <c r="Q6">
-        <v>0.002003402003402004</v>
-      </c>
-      <c r="R6">
-        <v>0.1796610169491525</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="V6">
-        <v>0.008769608769608769</v>
-      </c>
-      <c r="W6">
-        <v>0.05521759475900796</v>
-      </c>
-      <c r="X6">
-        <v>0.05421102243922741</v>
-      </c>
-      <c r="Y6">
-        <v>0.001006572319780553</v>
-      </c>
-      <c r="Z6">
-        <v>-35.96571520334016</v>
-      </c>
-      <c r="AA6">
-        <v>0.004685026830998166</v>
-      </c>
-      <c r="AB6">
-        <v>0.05355272255859517</v>
-      </c>
-      <c r="AC6">
-        <v>-0.04886769572759701</v>
-      </c>
-      <c r="AD6">
-        <v>24.8</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>24.8</v>
-      </c>
-      <c r="AG6">
-        <v>15.52</v>
-      </c>
-      <c r="AH6">
-        <v>0.02289935364727608</v>
-      </c>
-      <c r="AI6">
-        <v>0.08449744463373084</v>
-      </c>
-      <c r="AJ6">
-        <v>0.01445442014677942</v>
-      </c>
-      <c r="AK6">
-        <v>0.05460558722116671</v>
-      </c>
-      <c r="AL6">
-        <v>1.22</v>
-      </c>
-      <c r="AM6">
-        <v>1.22</v>
-      </c>
-      <c r="AN6">
-        <v>-12.91666666666667</v>
-      </c>
-      <c r="AO6">
-        <v>0.9754098360655737</v>
-      </c>
-      <c r="AP6">
-        <v>-8.083333333333334</v>
-      </c>
-      <c r="AQ6">
-        <v>0.9754098360655737</v>
+        <v>6.060716612377851</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/china/china_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/china/china_insurance_prop_cas.xlsx
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0654</v>
+        <v>0.05405</v>
       </c>
       <c r="E2">
-        <v>0.07035</v>
+        <v>0.0673</v>
       </c>
       <c r="F2">
         <v>0.119</v>
       </c>
       <c r="G2">
-        <v>0.05764986292469311</v>
+        <v>0.06004865941132331</v>
       </c>
       <c r="H2">
-        <v>0.05764986292469311</v>
+        <v>0.06004865941132331</v>
       </c>
       <c r="I2">
-        <v>0.05514438488491974</v>
+        <v>0.04541832563589306</v>
       </c>
       <c r="J2">
-        <v>0.04672996661770633</v>
+        <v>0.04043044274189792</v>
       </c>
       <c r="K2">
-        <v>7117.8</v>
+        <v>6664.9</v>
       </c>
       <c r="L2">
-        <v>0.04719103358427894</v>
+        <v>0.04422008597336406</v>
       </c>
       <c r="M2">
-        <v>2127.5</v>
+        <v>2302.4</v>
       </c>
       <c r="N2">
-        <v>0.04179567171685421</v>
+        <v>0.04316978415107924</v>
       </c>
       <c r="O2">
-        <v>0.2988985360645143</v>
+        <v>0.3454515446593347</v>
       </c>
       <c r="P2">
-        <v>2127.5</v>
+        <v>2302.4</v>
       </c>
       <c r="Q2">
-        <v>0.04179567171685421</v>
+        <v>0.04316978415107924</v>
       </c>
       <c r="R2">
-        <v>0.2988985360645143</v>
+        <v>0.3454515446593347</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4452.3</v>
+        <v>3979.7</v>
       </c>
       <c r="V2">
-        <v>0.08746738857106934</v>
+        <v>0.07461900190499048</v>
       </c>
       <c r="W2">
-        <v>0.1127553934927922</v>
+        <v>0.1048216312552654</v>
       </c>
       <c r="X2">
-        <v>0.1023650873741052</v>
+        <v>0.08839542801070051</v>
       </c>
       <c r="Y2">
-        <v>0.01039030611868698</v>
+        <v>0.01642620324456485</v>
       </c>
       <c r="Z2">
-        <v>1.797476636182277</v>
+        <v>1.91533425337837</v>
       </c>
       <c r="AA2">
-        <v>0.08465892576715235</v>
+        <v>0.07995921239587789</v>
       </c>
       <c r="AB2">
-        <v>0.08580520255436383</v>
+        <v>0.07352084497297741</v>
       </c>
       <c r="AC2">
-        <v>-0.001146276787211485</v>
+        <v>0.006438367422900472</v>
       </c>
       <c r="AD2">
-        <v>21211.6</v>
+        <v>23849</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>21211.6</v>
+        <v>23849</v>
       </c>
       <c r="AG2">
-        <v>16759.3</v>
+        <v>19869.3</v>
       </c>
       <c r="AH2">
-        <v>0.2941398341514824</v>
+        <v>0.3089945143076289</v>
       </c>
       <c r="AI2">
-        <v>0.2240791369642472</v>
+        <v>0.2378281243299897</v>
       </c>
       <c r="AJ2">
-        <v>0.2476925646266647</v>
+        <v>0.2714277713041423</v>
       </c>
       <c r="AK2">
-        <v>0.1857832209460485</v>
+        <v>0.206330102410627</v>
       </c>
       <c r="AL2">
-        <v>916.2</v>
+        <v>1385.8</v>
       </c>
       <c r="AM2">
-        <v>916.2</v>
+        <v>1385.8</v>
       </c>
       <c r="AN2">
-        <v>2.346052602473068</v>
+        <v>3.145144273882998</v>
       </c>
       <c r="AO2">
-        <v>9.078148875791314</v>
+        <v>4.939745995093087</v>
       </c>
       <c r="AP2">
-        <v>1.853617802552702</v>
+        <v>2.620311758189587</v>
       </c>
       <c r="AQ2">
-        <v>9.078148875791314</v>
+        <v>4.939745995093087</v>
       </c>
     </row>
     <row r="3">
@@ -725,49 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0747</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="E3">
-        <v>0.0506</v>
+        <v>0.0696</v>
       </c>
       <c r="F3">
-        <v>0.119</v>
+        <v>0.107</v>
       </c>
       <c r="G3">
-        <v>0.06135823160550052</v>
+        <v>0.06601437315665606</v>
       </c>
       <c r="H3">
-        <v>0.06135823160550052</v>
+        <v>0.06601437315665606</v>
       </c>
       <c r="I3">
-        <v>0.0569406626042843</v>
+        <v>0.05815154080302407</v>
       </c>
       <c r="J3">
-        <v>0.04919966480653237</v>
+        <v>0.05025277673876542</v>
       </c>
       <c r="K3">
-        <v>3716.8</v>
+        <v>3825.5</v>
       </c>
       <c r="L3">
-        <v>0.0577328426994391</v>
+        <v>0.06030325815721566</v>
       </c>
       <c r="M3">
-        <v>1245.2</v>
+        <v>1248.3</v>
       </c>
       <c r="N3">
-        <v>0.05890812754281389</v>
+        <v>0.04724275349977861</v>
       </c>
       <c r="O3">
-        <v>0.3350193715023676</v>
+        <v>0.3263102862370932</v>
       </c>
       <c r="P3">
-        <v>1245.2</v>
+        <v>1248.3</v>
       </c>
       <c r="Q3">
-        <v>0.05890812754281389</v>
+        <v>0.04724275349977861</v>
       </c>
       <c r="R3">
-        <v>0.3350193715023676</v>
+        <v>0.3263102862370932</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,73 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1685.5</v>
+        <v>1249.4</v>
       </c>
       <c r="V3">
-        <v>0.07973791276374302</v>
+        <v>0.04728438373998509</v>
       </c>
       <c r="W3">
-        <v>0.1231299277810906</v>
+        <v>0.1238286370919449</v>
       </c>
       <c r="X3">
-        <v>0.09482456049449245</v>
+        <v>0.0816849371058449</v>
       </c>
       <c r="Y3">
-        <v>0.02830536728659813</v>
+        <v>0.0421436999861</v>
       </c>
       <c r="Z3">
-        <v>1.829045720958114</v>
+        <v>1.923193757275902</v>
       </c>
       <c r="AA3">
-        <v>0.08998843638696156</v>
+        <v>0.09664582650977331</v>
       </c>
       <c r="AB3">
-        <v>0.08680738240220134</v>
+        <v>0.07453449740217515</v>
       </c>
       <c r="AC3">
-        <v>0.003181053984760221</v>
+        <v>0.02211132910759817</v>
       </c>
       <c r="AD3">
-        <v>3777.6</v>
+        <v>5399.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3777.6</v>
+        <v>5399.7</v>
       </c>
       <c r="AG3">
-        <v>2092.1</v>
+        <v>4150.299999999999</v>
       </c>
       <c r="AH3">
-        <v>0.1516158551269084</v>
+        <v>0.1696802292695803</v>
       </c>
       <c r="AI3">
-        <v>0.1076681031534305</v>
+        <v>0.1451852290020919</v>
       </c>
       <c r="AJ3">
-        <v>0.09005987920844077</v>
+        <v>0.1357487227459164</v>
       </c>
       <c r="AK3">
-        <v>0.06263753701336224</v>
+        <v>0.115470864494302</v>
       </c>
       <c r="AL3">
-        <v>148.7</v>
+        <v>183.3</v>
       </c>
       <c r="AM3">
-        <v>148.7</v>
+        <v>183.3</v>
       </c>
       <c r="AN3">
-        <v>0.9368815257558096</v>
+        <v>1.328829826504245</v>
       </c>
       <c r="AO3">
-        <v>24.65232010759919</v>
+        <v>20.12547735951991</v>
       </c>
       <c r="AP3">
-        <v>0.5188611393566628</v>
+        <v>1.0213608957795</v>
       </c>
       <c r="AQ3">
-        <v>24.65232010759919</v>
+        <v>20.12547735951991</v>
       </c>
     </row>
     <row r="4">
@@ -862,46 +862,49 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0561</v>
+        <v>0.0521</v>
       </c>
       <c r="E4">
-        <v>0.0901</v>
+        <v>0.065</v>
+      </c>
+      <c r="F4">
+        <v>0.131</v>
       </c>
       <c r="G4">
-        <v>0.05488824780046779</v>
+        <v>0.05571277012582004</v>
       </c>
       <c r="H4">
-        <v>0.05488824780046779</v>
+        <v>0.05571277012582004</v>
       </c>
       <c r="I4">
-        <v>0.05380670027368358</v>
+        <v>0.03616380663448033</v>
       </c>
       <c r="J4">
-        <v>0.04470103556475404</v>
+        <v>0.03313287557079521</v>
       </c>
       <c r="K4">
-        <v>3401</v>
+        <v>2839.4</v>
       </c>
       <c r="L4">
-        <v>0.03934056832719878</v>
+        <v>0.03253081341927561</v>
       </c>
       <c r="M4">
-        <v>882.3</v>
+        <v>1054.1</v>
       </c>
       <c r="N4">
-        <v>0.02964279474808832</v>
+        <v>0.03917058397279872</v>
       </c>
       <c r="O4">
-        <v>0.2594236989120847</v>
+        <v>0.3712404029020215</v>
       </c>
       <c r="P4">
-        <v>882.3</v>
+        <v>1054.1</v>
       </c>
       <c r="Q4">
-        <v>0.02964279474808832</v>
+        <v>0.03917058397279872</v>
       </c>
       <c r="R4">
-        <v>0.2594236989120847</v>
+        <v>0.3712404029020215</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -910,73 +913,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2766.8</v>
+        <v>2730.3</v>
       </c>
       <c r="V4">
-        <v>0.09295668651140289</v>
+        <v>0.101458538488694</v>
       </c>
       <c r="W4">
-        <v>0.1023808592044938</v>
+        <v>0.08581462541858582</v>
       </c>
       <c r="X4">
-        <v>0.109905614253718</v>
+        <v>0.09510591891555611</v>
       </c>
       <c r="Y4">
-        <v>-0.007524755049224188</v>
+        <v>-0.00929129349697029</v>
       </c>
       <c r="Z4">
-        <v>1.774666160304638</v>
+        <v>1.909662146492161</v>
       </c>
       <c r="AA4">
-        <v>0.07932941514734314</v>
+        <v>0.06327259828198245</v>
       </c>
       <c r="AB4">
-        <v>0.08480302270652633</v>
+        <v>0.07250719254377967</v>
       </c>
       <c r="AC4">
-        <v>-0.005473607559183191</v>
+        <v>-0.009234594261797222</v>
       </c>
       <c r="AD4">
-        <v>17434</v>
+        <v>18449.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>17434</v>
+        <v>18449.3</v>
       </c>
       <c r="AG4">
-        <v>14667.2</v>
+        <v>15719</v>
       </c>
       <c r="AH4">
-        <v>0.3693769280314587</v>
+        <v>0.4067323929999691</v>
       </c>
       <c r="AI4">
-        <v>0.2926365827620704</v>
+        <v>0.292444500804451</v>
       </c>
       <c r="AJ4">
-        <v>0.3301074010389002</v>
+        <v>0.3687352654851687</v>
       </c>
       <c r="AK4">
-        <v>0.2581853515652505</v>
+        <v>0.260437204462839</v>
       </c>
       <c r="AL4">
-        <v>767.5</v>
+        <v>1202.5</v>
       </c>
       <c r="AM4">
-        <v>767.5</v>
+        <v>1202.5</v>
       </c>
       <c r="AN4">
-        <v>3.480326592537879</v>
+        <v>5.242320916091268</v>
       </c>
       <c r="AO4">
-        <v>6.060716612377851</v>
+        <v>2.624948024948025</v>
       </c>
       <c r="AP4">
-        <v>2.927993931287805</v>
+        <v>4.466513227062199</v>
       </c>
       <c r="AQ4">
-        <v>6.060716612377851</v>
+        <v>2.624948024948025</v>
       </c>
     </row>
   </sheetData>
